--- a/Sim/Scenario_H2_Figures/tables_output_summary_2035.xlsx
+++ b/Sim/Scenario_H2_Figures/tables_output_summary_2035.xlsx
@@ -424,16 +424,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="C2">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="D2">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="E2">
-        <v>3.94</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -441,13 +441,13 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="C3">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="D3">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="E3">
         <v>2.82</v>
@@ -461,10 +461,10 @@
         <v>0.74</v>
       </c>
       <c r="C4">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="D4">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="E4">
         <v>1.46</v>
@@ -475,13 +475,13 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>4.42</v>
+        <v>3.87</v>
       </c>
       <c r="C5">
-        <v>4.42</v>
+        <v>3.88</v>
       </c>
       <c r="D5">
-        <v>4.41</v>
+        <v>3.89</v>
       </c>
       <c r="E5">
         <v>4.7</v>
@@ -519,16 +519,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1649</v>
+        <v>1510</v>
       </c>
       <c r="C2">
-        <v>1673</v>
+        <v>1494</v>
       </c>
       <c r="D2">
-        <v>1695</v>
+        <v>1471</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -536,13 +536,13 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>3116</v>
+        <v>2454</v>
       </c>
       <c r="C3">
-        <v>3004</v>
+        <v>2368</v>
       </c>
       <c r="D3">
-        <v>2882</v>
+        <v>2269</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -556,13 +556,13 @@
         <v>1553</v>
       </c>
       <c r="C4">
-        <v>1543</v>
+        <v>1518</v>
       </c>
       <c r="D4">
-        <v>1527</v>
+        <v>1475</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -570,13 +570,13 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>4558</v>
+        <v>2789</v>
       </c>
       <c r="C5">
-        <v>4398</v>
+        <v>2691</v>
       </c>
       <c r="D5">
-        <v>4213</v>
+        <v>2578</v>
       </c>
       <c r="E5">
         <v>0</v>
